--- a/artfynd/A 41718-2021 artfynd.xlsx
+++ b/artfynd/A 41718-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41718-2021 artfynd.xlsx
+++ b/artfynd/A 41718-2021 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>131034596</v>
       </c>
       <c r="B4" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41718-2021 artfynd.xlsx
+++ b/artfynd/A 41718-2021 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>131034596</v>
       </c>
       <c r="B4" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41718-2021 artfynd.xlsx
+++ b/artfynd/A 41718-2021 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>131034596</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41718-2021 artfynd.xlsx
+++ b/artfynd/A 41718-2021 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>131034596</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41718-2021 artfynd.xlsx
+++ b/artfynd/A 41718-2021 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>131034596</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41718-2021 artfynd.xlsx
+++ b/artfynd/A 41718-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63266967</v>
+        <v>63266485</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -713,17 +708,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SO Römmarsmyran, Dlr</t>
+          <t>SO Römmarsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520210.9993824648</v>
+        <v>520384</v>
       </c>
       <c r="R2" t="n">
-        <v>6745989.952245037</v>
+        <v>6745829</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,24 +745,14 @@
           <t>2017-02-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-02-04</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På en äldre tall. Ca 200 m SO Römmarsmyran.</t>
+          <t>På flera äldre tallar, 10-tal. Ca 450 m SO Rö-myran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,19 +779,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63266485</v>
+        <v>63266967</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -832,17 +812,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>SO Römmarsmyren, Dlr</t>
+          <t>SO Römmarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520383.7587504648</v>
+        <v>520211</v>
       </c>
       <c r="R3" t="n">
-        <v>6745829.114723548</v>
+        <v>6745990</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,24 +849,14 @@
           <t>2017-02-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-02-04</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På flera äldre tallar, 10-tal. Ca 450 m SO Rö-myran.</t>
+          <t>På en äldre tall. Ca 200 m SO Römmarsmyran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,11 +886,11 @@
         <v>131034596</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1007,6 +977,115 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>63266223</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SO Römmarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>520407</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6745776</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-02-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-02-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Under 2 äldre tallar. Ca. 500 m SO Rö-myran.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41718-2021 artfynd.xlsx
+++ b/artfynd/A 41718-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63266485</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63266967</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131034596</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,8 +1106,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63266223</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>